--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.31216787177549</v>
+        <v>4.763227279163518</v>
       </c>
       <c r="D2" t="n">
-        <v>29.10104362378142</v>
+        <v>4.728919588864481</v>
       </c>
       <c r="E2" t="n">
-        <v>13.65747436597176</v>
+        <v>2.219339584470412</v>
       </c>
       <c r="F2" t="n">
-        <v>13.65155438475433</v>
+        <v>2.21837758752258</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.079472530743611</v>
+        <v>1.150414286245837</v>
       </c>
       <c r="D3" t="n">
-        <v>6.878183136791651</v>
+        <v>1.117704759728643</v>
       </c>
       <c r="E3" t="n">
-        <v>13.65747436597176</v>
+        <v>2.219339584470412</v>
       </c>
       <c r="F3" t="n">
-        <v>13.65155438475433</v>
+        <v>2.21837758752258</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.3481233800792</v>
+        <v>3.46907004926287</v>
       </c>
       <c r="D4" t="n">
-        <v>21.14956958405725</v>
+        <v>3.436805057409303</v>
       </c>
       <c r="E4" t="n">
-        <v>13.65747436597176</v>
+        <v>2.219339584470412</v>
       </c>
       <c r="F4" t="n">
-        <v>13.65155438475433</v>
+        <v>2.21837758752258</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.40965405068593</v>
+        <v>4.616568783236464</v>
       </c>
       <c r="D5" t="n">
-        <v>28.21474640566975</v>
+        <v>4.584896290921335</v>
       </c>
       <c r="E5" t="n">
-        <v>13.65747436597176</v>
+        <v>2.219339584470412</v>
       </c>
       <c r="F5" t="n">
-        <v>13.65155438475433</v>
+        <v>2.21837758752258</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.556480317765107</v>
+        <v>1.22792805163683</v>
       </c>
       <c r="D6" t="n">
-        <v>7.543155374596011</v>
+        <v>1.225762748371852</v>
       </c>
       <c r="E6" t="n">
-        <v>13.65747436597176</v>
+        <v>2.219339584470412</v>
       </c>
       <c r="F6" t="n">
-        <v>13.65155438475433</v>
+        <v>2.21837758752258</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.49239907317474</v>
+        <v>6.905014849390895</v>
       </c>
       <c r="D7" t="n">
-        <v>42.70168047423456</v>
+        <v>6.939023077063116</v>
       </c>
       <c r="E7" t="n">
-        <v>13.65747436597176</v>
+        <v>2.219339584470412</v>
       </c>
       <c r="F7" t="n">
-        <v>13.65155438475433</v>
+        <v>2.21837758752258</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.73165839354128</v>
+        <v>3.856394488950458</v>
       </c>
       <c r="D8" t="n">
-        <v>23.8694678453914</v>
+        <v>3.878788524876103</v>
       </c>
       <c r="E8" t="n">
-        <v>13.65747436597176</v>
+        <v>2.219339584470412</v>
       </c>
       <c r="F8" t="n">
-        <v>13.65155438475433</v>
+        <v>2.21837758752258</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.26048356077276</v>
+        <v>5.242328578625573</v>
       </c>
       <c r="D9" t="n">
-        <v>32.24524289319493</v>
+        <v>5.239851970144175</v>
       </c>
       <c r="E9" t="n">
-        <v>13.65747436597176</v>
+        <v>2.219339584470412</v>
       </c>
       <c r="F9" t="n">
-        <v>13.65155438475433</v>
+        <v>2.21837758752258</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.63400131489895</v>
+        <v>4.00302521367108</v>
       </c>
       <c r="D10" t="n">
-        <v>24.74060738429707</v>
+        <v>4.020348699948274</v>
       </c>
       <c r="E10" t="n">
-        <v>13.65747436597176</v>
+        <v>2.219339584470412</v>
       </c>
       <c r="F10" t="n">
-        <v>13.65155438475433</v>
+        <v>2.21837758752258</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>55.97283894344383</v>
+        <v>9.095586328309624</v>
       </c>
       <c r="D11" t="n">
-        <v>56.00509771492289</v>
+        <v>9.10082837867497</v>
       </c>
       <c r="E11" t="n">
-        <v>13.65747436597176</v>
+        <v>2.219339584470412</v>
       </c>
       <c r="F11" t="n">
-        <v>13.65155438475433</v>
+        <v>2.21837758752258</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>50.98591964952011</v>
+        <v>8.285211943047017</v>
       </c>
       <c r="D12" t="n">
-        <v>50.71062806884849</v>
+        <v>8.24047706118788</v>
       </c>
       <c r="E12" t="n">
-        <v>13.65747436597176</v>
+        <v>2.219339584470412</v>
       </c>
       <c r="F12" t="n">
-        <v>13.65155438475433</v>
+        <v>2.21837758752258</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.07818535790933</v>
+        <v>5.050205120660266</v>
       </c>
       <c r="D13" t="n">
-        <v>30.86381543643205</v>
+        <v>5.015370008420208</v>
       </c>
       <c r="E13" t="n">
-        <v>13.65747436597176</v>
+        <v>2.219339584470412</v>
       </c>
       <c r="F13" t="n">
-        <v>13.65155438475433</v>
+        <v>2.21837758752258</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>40.13890281602596</v>
+        <v>6.522571707604219</v>
       </c>
       <c r="D14" t="n">
-        <v>40.00501357468975</v>
+        <v>6.500814705887084</v>
       </c>
       <c r="E14" t="n">
-        <v>13.65747436597176</v>
+        <v>2.219339584470412</v>
       </c>
       <c r="F14" t="n">
-        <v>13.65155438475433</v>
+        <v>2.21837758752258</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>38.29902741174861</v>
+        <v>6.22359195440915</v>
       </c>
       <c r="D15" t="n">
-        <v>37.75303290028099</v>
+        <v>6.13486784629566</v>
       </c>
       <c r="E15" t="n">
-        <v>13.65747436597176</v>
+        <v>2.219339584470412</v>
       </c>
       <c r="F15" t="n">
-        <v>13.65155438475433</v>
+        <v>2.21837758752258</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
